--- a/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -79,21 +79,51 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>DECTOR</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>ROCHA</t>
   </si>
   <si>
@@ -103,22 +133,46 @@
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>DAVID</t>
   </si>
   <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
     <t>AZURA</t>
   </si>
   <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -711,16 +765,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -734,16 +791,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +920,7 @@
         <v>83.33</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -877,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>95.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,10 +994,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,22 +1011,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920230</v>
+        <v>22330051920201</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -974,39 +1034,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920192</v>
+        <v>22330051920357</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920236</v>
+        <v>22330051920369</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1015,21 +1075,21 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920243</v>
+        <v>22330051920366</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1038,29 +1098,190 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920257</v>
+        <v>22330051920192</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920371</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920236</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920253</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920257</v>
+      </c>
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G7">
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -94,12 +94,6 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -124,15 +118,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -161,15 +146,6 @@
   </si>
   <si>
     <t>ERIK</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
   </si>
   <si>
     <t>NOEMI DEL ROCIO</t>
@@ -719,16 +695,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -742,16 +721,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -765,16 +747,16 @@
         <v>18</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
       <c r="F4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -791,16 +773,16 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>95.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -859,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
       <c r="G2">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -885,16 +867,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>64.29000000000001</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -920,7 +902,7 @@
         <v>83.33</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -956,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -994,10 +976,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1017,10 +999,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1040,10 +1022,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1063,10 +1045,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1086,10 +1068,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1112,7 +1094,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1132,10 +1114,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1155,10 +1137,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1172,16 +1154,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920230</v>
+        <v>22330051920253</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1195,16 +1177,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920236</v>
+        <v>22330051920257</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1213,75 +1195,6 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920243</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920253</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920257</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -79,15 +79,36 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -100,6 +121,30 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -122,6 +167,33 @@
   </si>
   <si>
     <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
   </si>
   <si>
     <t>DAVID</t>
@@ -938,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -970,131 +1042,131 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920188</v>
+        <v>22330051920405</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920201</v>
+        <v>22330051920279</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920357</v>
+        <v>21330051920133</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920369</v>
+        <v>22330051920177</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920366</v>
+        <v>21330051920007</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920192</v>
+        <v>22330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1103,21 +1175,21 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920371</v>
+        <v>22330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1126,21 +1198,21 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920202</v>
+        <v>22330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1149,21 +1221,21 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920253</v>
+        <v>21330051420317</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1172,29 +1244,236 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>22330051920188</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920201</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920357</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920369</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920366</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920192</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920371</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920202</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920253</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
         <v>22330051920257</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>10</v>
       </c>
-      <c r="G11">
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -76,51 +76,48 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
@@ -130,45 +127,33 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>NOLASCO</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
     <t>JONATAN GILBERTO</t>
   </si>
   <si>
@@ -181,43 +166,13 @@
     <t>MARCO</t>
   </si>
   <si>
-    <t>YOLET</t>
+    <t>DAVID</t>
   </si>
   <si>
     <t>ARACELY</t>
   </si>
   <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ERIK</t>
   </si>
   <si>
     <t>NOEMI DEL ROCIO</t>
@@ -621,10 +576,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>9</v>
@@ -633,7 +588,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="H2">
         <v>5.5</v>
@@ -699,10 +654,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -711,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="G5">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -764,10 +719,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>11</v>
@@ -776,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="H2">
         <v>5.5</v>
@@ -842,10 +797,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -854,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -907,22 +862,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>76.19</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -985,10 +940,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -997,7 +952,7 @@
         <v>23</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
         <v>8.300000000000001</v>
@@ -1010,7 +965,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,22 +997,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920405</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1065,154 +1020,154 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920279</v>
+        <v>22330051920369</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920133</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920177</v>
+        <v>22330051920357</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920007</v>
+        <v>22330051920405</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920190</v>
+        <v>22330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920359</v>
+        <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920193</v>
+        <v>22330051920177</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1221,44 +1176,44 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051420317</v>
+        <v>22330051920188</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1267,21 +1222,21 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920201</v>
+        <v>22330051920193</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1290,21 +1245,21 @@
         <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920357</v>
+        <v>22330051920253</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1313,21 +1268,21 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920369</v>
+        <v>22330051920257</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1336,144 +1291,6 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920366</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920192</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920371</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920202</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920253</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920257</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -76,52 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>CABRERA</t>
@@ -136,31 +106,7 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
+    <t>ANGELA</t>
   </si>
   <si>
     <t>MARCO</t>
@@ -173,12 +119,6 @@
   </si>
   <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
 </sst>
 </file>
@@ -894,16 +834,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>82.14</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -920,16 +860,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -955,7 +895,7 @@
         <v>95.83</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +905,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,22 +937,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051420317</v>
+        <v>22330051920225</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1020,277 +960,93 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920369</v>
+        <v>22330051920177</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920188</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920357</v>
+        <v>22330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920405</v>
+        <v>22330051920193</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920279</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920177</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920188</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920190</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920193</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920253</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920257</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
     <t>CAMPOS</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -104,9 +98,6 @@
   </si>
   <si>
     <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
   </si>
   <si>
     <t>MARCO</t>
@@ -519,19 +510,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -597,19 +588,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -662,19 +653,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>42.86</v>
+        <v>47.62</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,19 +731,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -805,19 +796,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -883,19 +874,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -937,39 +928,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920225</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920177</v>
+        <v>22330051920188</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -983,16 +974,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1006,16 +997,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920190</v>
+        <v>22330051920193</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1024,29 +1015,6 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920193</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>
